--- a/templates/bain_p2p_coe_assessment_v1.xlsx
+++ b/templates/bain_p2p_coe_assessment_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://strategystackconsulting-my.sharepoint.com/personal/sudhakar_ghantasala_strategystackconsulting_com/Documents/Documents/StrategyStack/Projects/Bain/Generic AI Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_7C6DB5DBBA6329244DF325D635E950E3B1343E43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9255E778-D000-4258-A98C-555D069187AD}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="11_7C6DB5DBBA6329244DF325D635E950E3B1343E43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5673ED8-9343-4EB6-BA62-991EC243E49A}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="14400" windowHeight="8170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="assessment_meta" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
   <si>
     <t>field</t>
   </si>
@@ -65,18 +65,6 @@
     <t>Process</t>
   </si>
   <si>
-    <t>Describe the current organisation structure for this process/function.</t>
-  </si>
-  <si>
-    <t>How clearly are roles, responsibilities, and KPIs defined for key roles?</t>
-  </si>
-  <si>
-    <t>Describe the end-to-end process flow (key steps, variants, exceptions).</t>
-  </si>
-  <si>
-    <t>What are the top 3 pain points or bottlenecks you experience?</t>
-  </si>
-  <si>
     <t>Who owns what, and how are teams structured?</t>
   </si>
   <si>
@@ -86,13 +74,157 @@
     <t>Technology</t>
   </si>
   <si>
-    <t>What are all the technologies that are used currently in Bain?</t>
-  </si>
-  <si>
     <t>technology list</t>
   </si>
   <si>
-    <t>List issues with your netsuite ERP</t>
+    <t>Describe the current P2P organisation structure across entities. Who owns what?</t>
+  </si>
+  <si>
+    <t>How clearly are job roles and responsibilities defined for P2P-related positions?</t>
+  </si>
+  <si>
+    <t>How well do procurement, finance/AP, and site/operations teams collaborate in the P2P process?</t>
+  </si>
+  <si>
+    <t>Where do you see duplication of effort or unclear ownership in P2P today?</t>
+  </si>
+  <si>
+    <t>Describe current spans of control (manager-to-staff ratios) for P2P teams. Any issues?</t>
+  </si>
+  <si>
+    <t>Is workload balanced across team members, or are certain roles/people always overloaded?</t>
+  </si>
+  <si>
+    <t>How would you describe the team’s procurement skills (e.g., category knowledge, negotiation, RFQ)?</t>
+  </si>
+  <si>
+    <t>How would you describe the AP team’s skills for invoice processing, matching and reconciliation?</t>
+  </si>
+  <si>
+    <t>What formal training exists for onboarding and upskilling P2P staff (if any)?</t>
+  </si>
+  <si>
+    <t>How familiar are teams with ERP, workflows, and compliance policies related to P2P?</t>
+  </si>
+  <si>
+    <t>Has attrition or churn impacted process stability or knowledge retention in P2P?</t>
+  </si>
+  <si>
+    <t>Do team members clearly understand the P2P KPIs/SLAs they are accountable for?</t>
+  </si>
+  <si>
+    <t>How often are P2P performance reviews held, and how are results communicated?</t>
+  </si>
+  <si>
+    <t>Is there cross-training or backup coverage for key P2P roles? Describe gaps if any.</t>
+  </si>
+  <si>
+    <t>Describe how purchase requisitions (PRs) are created today (who, how, and with what quality).</t>
+  </si>
+  <si>
+    <t>What are the most common issues/errors with PRs (missing data, wrong codes, etc.)?</t>
+  </si>
+  <si>
+    <t>Is there a standard PR-to-approval process followed consistently across entities? Where does it differ?</t>
+  </si>
+  <si>
+    <t>How are purchase orders (POs) created and approved? Are there any manual/off-system POs?</t>
+  </si>
+  <si>
+    <t>How standardized is vendor onboarding (steps, checks, documentation)?</t>
+  </si>
+  <si>
+    <t>How are vendor validations (KYC, tax IDs, banking, compliance) carried out and recorded?</t>
+  </si>
+  <si>
+    <t>Describe the process for vendor master creation, updates, and deactivation. Any issues?</t>
+  </si>
+  <si>
+    <t>Describe how GRNs (goods receipts) are done. Where do delays or gaps typically occur?</t>
+  </si>
+  <si>
+    <t>How are services (non-materials) receipted and approved today?</t>
+  </si>
+  <si>
+    <t>Describe how invoices are received (channels), validated, and matched (2-way / 3-way).</t>
+  </si>
+  <si>
+    <t>What are the top recurring reasons for invoice mismatch, holds, or rework?</t>
+  </si>
+  <si>
+    <t>How is the payment cycle managed (terms, early/late payments, exceptions)?</t>
+  </si>
+  <si>
+    <t>Describe the approval matrix and escalation paths for P2P. Any informal workarounds?</t>
+  </si>
+  <si>
+    <t>How is the delegation of authority (DoA) maintained and updated?</t>
+  </si>
+  <si>
+    <t>How are P2P process exceptions tracked (e.g., manual holds, off-cycle payments, urgent requests)?</t>
+  </si>
+  <si>
+    <t>What internal or external audit observations have you had related to P2P in the last 2–3 years?</t>
+  </si>
+  <si>
+    <t>How different are P2P processes across countries/entities/business units?</t>
+  </si>
+  <si>
+    <t>Where is P2P process documentation (SOPs, process maps) stored, and how up-to-date is it?</t>
+  </si>
+  <si>
+    <t>How are non-PO invoices handled and controlled? Any risks?</t>
+  </si>
+  <si>
+    <t>How are key cycle times (PR-to-PO, GRN, invoice processing, payment) measured and reported today?</t>
+  </si>
+  <si>
+    <t>Which ERP and related systems support your P2P process (per entity)?</t>
+  </si>
+  <si>
+    <t>To what extent is the P2P flow (PR → PO → GRN → Invoice → Payment) executed fully in system vs. outside?</t>
+  </si>
+  <si>
+    <t>Describe how approval workflows are configured in the system. Any known gaps or pain points?</t>
+  </si>
+  <si>
+    <t>How are vendor masters maintained across systems? Any duplication or sync issues?</t>
+  </si>
+  <si>
+    <t>Describe key integrations (ERP ↔ HR, ERP ↔ banking, ERP ↔ other finance/procurement tools). Any failures?</t>
+  </si>
+  <si>
+    <t>What automation tools (OCR, RPA, workflow tools) exist for P2P today? How effectively are they used?</t>
+  </si>
+  <si>
+    <t>How automated is invoice capture and data entry vs. manual keying?</t>
+  </si>
+  <si>
+    <t>Describe master data quality (vendors, items, GLs, cost centers). Where do you see errors?</t>
+  </si>
+  <si>
+    <t>What standard reports or dashboards are available today for P2P KPIs and cycle times?</t>
+  </si>
+  <si>
+    <t>Do teams rely more on system reports or offline Excel sheets for tracking and analysis?</t>
+  </si>
+  <si>
+    <t>How are system incidents (bugs, downtime, performance issues) logged and resolved?</t>
+  </si>
+  <si>
+    <t>How are user access roles defined for P2P? Any known SoD (segregation of duties) gaps?</t>
+  </si>
+  <si>
+    <t>Does the ERP/system support robust 2-way and 3-way matching? Any limitations?</t>
+  </si>
+  <si>
+    <t>How are exceptions (e.g., unmatched invoices, blocked payments) flagged and routed in the system?</t>
+  </si>
+  <si>
+    <t>Are there any known system constraints that force manual workarounds in P2P? Describe them.</t>
+  </si>
+  <si>
+    <t>How easily can you extract an audit trail (who approved what, when) from systems for P2P?</t>
   </si>
 </sst>
 </file>
@@ -506,7 +638,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
@@ -534,13 +666,13 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -548,7 +680,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -556,24 +688,24 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -581,26 +713,510 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51">
         <v>1</v>
       </c>
     </row>

--- a/templates/bain_p2p_coe_assessment_v1.xlsx
+++ b/templates/bain_p2p_coe_assessment_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://strategystackconsulting-my.sharepoint.com/personal/sudhakar_ghantasala_strategystackconsulting_com/Documents/Documents/StrategyStack/Projects/Bain/Generic AI Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="11_7C6DB5DBBA6329244DF325D635E950E3B1343E43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5673ED8-9343-4EB6-BA62-991EC243E49A}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="11_7C6DB5DBBA6329244DF325D635E950E3B1343E43" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14370F4E-8774-4C69-9BF0-582796250B0E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>field</t>
   </si>
@@ -98,48 +98,6 @@
     <t>How would you describe the team’s procurement skills (e.g., category knowledge, negotiation, RFQ)?</t>
   </si>
   <si>
-    <t>How would you describe the AP team’s skills for invoice processing, matching and reconciliation?</t>
-  </si>
-  <si>
-    <t>What formal training exists for onboarding and upskilling P2P staff (if any)?</t>
-  </si>
-  <si>
-    <t>How familiar are teams with ERP, workflows, and compliance policies related to P2P?</t>
-  </si>
-  <si>
-    <t>Has attrition or churn impacted process stability or knowledge retention in P2P?</t>
-  </si>
-  <si>
-    <t>Do team members clearly understand the P2P KPIs/SLAs they are accountable for?</t>
-  </si>
-  <si>
-    <t>How often are P2P performance reviews held, and how are results communicated?</t>
-  </si>
-  <si>
-    <t>Is there cross-training or backup coverage for key P2P roles? Describe gaps if any.</t>
-  </si>
-  <si>
-    <t>Describe how purchase requisitions (PRs) are created today (who, how, and with what quality).</t>
-  </si>
-  <si>
-    <t>What are the most common issues/errors with PRs (missing data, wrong codes, etc.)?</t>
-  </si>
-  <si>
-    <t>Is there a standard PR-to-approval process followed consistently across entities? Where does it differ?</t>
-  </si>
-  <si>
-    <t>How are purchase orders (POs) created and approved? Are there any manual/off-system POs?</t>
-  </si>
-  <si>
-    <t>How standardized is vendor onboarding (steps, checks, documentation)?</t>
-  </si>
-  <si>
-    <t>How are vendor validations (KYC, tax IDs, banking, compliance) carried out and recorded?</t>
-  </si>
-  <si>
-    <t>Describe the process for vendor master creation, updates, and deactivation. Any issues?</t>
-  </si>
-  <si>
     <t>Describe how GRNs (goods receipts) are done. Where do delays or gaps typically occur?</t>
   </si>
   <si>
@@ -162,51 +120,6 @@
   </si>
   <si>
     <t>How are P2P process exceptions tracked (e.g., manual holds, off-cycle payments, urgent requests)?</t>
-  </si>
-  <si>
-    <t>What internal or external audit observations have you had related to P2P in the last 2–3 years?</t>
-  </si>
-  <si>
-    <t>How different are P2P processes across countries/entities/business units?</t>
-  </si>
-  <si>
-    <t>Where is P2P process documentation (SOPs, process maps) stored, and how up-to-date is it?</t>
-  </si>
-  <si>
-    <t>How are non-PO invoices handled and controlled? Any risks?</t>
-  </si>
-  <si>
-    <t>How are key cycle times (PR-to-PO, GRN, invoice processing, payment) measured and reported today?</t>
-  </si>
-  <si>
-    <t>Which ERP and related systems support your P2P process (per entity)?</t>
-  </si>
-  <si>
-    <t>To what extent is the P2P flow (PR → PO → GRN → Invoice → Payment) executed fully in system vs. outside?</t>
-  </si>
-  <si>
-    <t>Describe how approval workflows are configured in the system. Any known gaps or pain points?</t>
-  </si>
-  <si>
-    <t>How are vendor masters maintained across systems? Any duplication or sync issues?</t>
-  </si>
-  <si>
-    <t>Describe key integrations (ERP ↔ HR, ERP ↔ banking, ERP ↔ other finance/procurement tools). Any failures?</t>
-  </si>
-  <si>
-    <t>What automation tools (OCR, RPA, workflow tools) exist for P2P today? How effectively are they used?</t>
-  </si>
-  <si>
-    <t>How automated is invoice capture and data entry vs. manual keying?</t>
-  </si>
-  <si>
-    <t>Describe master data quality (vendors, items, GLs, cost centers). Where do you see errors?</t>
-  </si>
-  <si>
-    <t>What standard reports or dashboards are available today for P2P KPIs and cycle times?</t>
-  </si>
-  <si>
-    <t>Do teams rely more on system reports or offline Excel sheets for tracking and analysis?</t>
   </si>
   <si>
     <t>How are system incidents (bugs, downtime, performance issues) logged and resolved?</t>
@@ -638,7 +551,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
@@ -749,7 +662,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
@@ -760,7 +673,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
@@ -771,7 +684,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
@@ -782,7 +695,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
@@ -793,7 +706,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
@@ -804,7 +717,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -815,7 +728,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -837,7 +750,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>33</v>
@@ -848,7 +761,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -859,7 +772,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
@@ -870,7 +783,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
         <v>36</v>
@@ -881,7 +794,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -892,331 +805,12 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" t="s">
-        <v>52</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" t="s">
-        <v>59</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" t="s">
-        <v>63</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>16</v>
-      </c>
-      <c r="B48" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>16</v>
-      </c>
-      <c r="B50" t="s">
-        <v>66</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51">
         <v>1</v>
       </c>
     </row>
